--- a/data/trans_dic/IP16B_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores vacunados de la triple vírica</t>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,42; 100,0</t>
+          <t>96,94; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96,1; 100,0</t>
+          <t>95,69; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,7; 99,72</t>
+          <t>97,46; 99,71</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,95; 99,45</t>
+          <t>93,52; 99,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,14; 98,01</t>
+          <t>91,67; 98,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,19; 98,29</t>
+          <t>94,18; 98,24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,12 +672,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,08; 100,0</t>
+          <t>96,16; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,1; 100,0</t>
+          <t>97,3; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,84; 98,75</t>
+          <t>90,95; 98,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,31; 100,0</t>
+          <t>93,79; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,21; 98,85</t>
+          <t>94,53; 98,97</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>97,23; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,34; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98,63; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95,79; 100,0</t>
+          <t>95,06; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>96,2; 100,0</t>
+          <t>97,22; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97,36; 100,0</t>
+          <t>97,55; 100,0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>94,82; 99,45</t>
+          <t>94,48; 99,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>95,69; 99,58</t>
+          <t>95,31; 99,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96,54; 99,28</t>
+          <t>96,73; 99,33</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>97,09; 100,0</t>
+          <t>96,88; 100,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>96,15; 99,54</t>
+          <t>96,05; 99,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,15; 99,38</t>
+          <t>97,39; 99,48</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>97,5; 99,04</t>
+          <t>97,54; 99,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>97,3; 98,86</t>
+          <t>97,35; 98,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97,72; 98,83</t>
+          <t>97,66; 98,78</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>72811</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78404</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>151215</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>71037; 73282</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75944; 79366</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148770; 152198</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>122444</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>121976</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>244420</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>117583; 124717</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>116601; 124801</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>238200; 248474</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>57871</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66401</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>124272</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>56031; 58268</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>64979; 66782</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>122232; 125050</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>63600</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68997</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>132597</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>60094; 65259</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>65881; 70241</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>128867; 134916</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>34513</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>40719</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>75232</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>45817</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>55828</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>101645</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>43886; 46167</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>54623; 56186</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>99844; 102353</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>120183</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>151519</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>271702</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>115627; 121700</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>146804; 153380</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>267372; 274541</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>130413</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>153337</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>283750</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>127515; 131619</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>149901; 155011</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>280166; 286181</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>647654</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>737181</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1384834</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>641840; 651686</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>730668; 741879</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1375720; 1391436</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,94; 100,0</t>
+          <t>96,86; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95,69; 100,0</t>
+          <t>96,18; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,46; 99,71</t>
+          <t>97,54; 99,72</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,52; 99,19</t>
+          <t>93,85; 99,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,67; 98,11</t>
+          <t>92,1; 98,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,18; 98,24</t>
+          <t>94,29; 98,34</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>96,16; 100,0</t>
+          <t>97,12; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,3; 100,0</t>
+          <t>96,14; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97,75; 100,0</t>
+          <t>97,79; 100,0</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,95; 98,76</t>
+          <t>91,81; 98,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,79; 100,0</t>
+          <t>92,64; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,53; 98,97</t>
+          <t>94,37; 98,86</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95,06; 100,0</t>
+          <t>96,11; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97,22; 100,0</t>
+          <t>97,1; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>94,48; 99,45</t>
+          <t>94,89; 99,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>95,31; 99,58</t>
+          <t>95,75; 99,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96,73; 99,33</t>
+          <t>96,59; 99,27</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>96,88; 100,0</t>
+          <t>96,74; 100,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>96,05; 99,33</t>
+          <t>96,28; 99,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,39; 99,48</t>
+          <t>97,32; 99,38</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,04</t>
+          <t>97,54; 99,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>97,35; 98,84</t>
+          <t>97,28; 98,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97,66; 98,78</t>
+          <t>97,68; 98,79</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>71037; 73282</t>
+          <t>70983; 73282</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75944; 79366</t>
+          <t>76337; 79366</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148770; 152198</t>
+          <t>148895; 152219</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>117583; 124717</t>
+          <t>117992; 124899</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>116601; 124801</t>
+          <t>117157; 124815</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>238200; 248474</t>
+          <t>238477; 248744</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56031; 58268</t>
+          <t>56589; 58268</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64979; 66782</t>
+          <t>64206; 66782</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122232; 125050</t>
+          <t>122291; 125050</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60094; 65259</t>
+          <t>60665; 65239</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65881; 70241</t>
+          <t>65074; 70241</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128867; 134916</t>
+          <t>128648; 134763</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43886; 46167</t>
+          <t>44369; 46167</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54623; 56186</t>
+          <t>54557; 56186</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>99844; 102353</t>
+          <t>99847; 102353</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>115627; 121700</t>
+          <t>116122; 121719</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>146804; 153380</t>
+          <t>147487; 153426</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>267372; 274541</t>
+          <t>266966; 274384</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>127515; 131619</t>
+          <t>127330; 131619</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>149901; 155011</t>
+          <t>150249; 155000</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>280166; 286181</t>
+          <t>279961; 285895</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>641840; 651686</t>
+          <t>641857; 651919</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>730668; 741879</t>
+          <t>730188; 741701</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1375720; 1391436</t>
+          <t>1375972; 1391602</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16B_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,86; 100,0</t>
+          <t>96,1; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96,18; 100,0</t>
+          <t>95,54; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,72</t>
+          <t>97,54; 99,7</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,85; 99,34</t>
+          <t>92,04; 98,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,1; 98,12</t>
+          <t>92,81; 99,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,29; 98,34</t>
+          <t>93,99; 98,24</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97,12; 100,0</t>
+          <t>97,27; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,14; 100,0</t>
+          <t>95,47; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97,79; 100,0</t>
+          <t>97,92; 100,0</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,81; 98,73</t>
+          <t>93,18; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,64; 100,0</t>
+          <t>91,96; 98,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,37; 98,86</t>
+          <t>94,98; 98,99</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>96,11; 100,0</t>
+          <t>96,96; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97,1; 100,0</t>
+          <t>96,79; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97,55; 100,0</t>
+          <t>97,88; 100,0</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>94,89; 99,46</t>
+          <t>95,53; 99,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>95,75; 99,61</t>
+          <t>94,65; 99,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96,59; 99,27</t>
+          <t>96,38; 99,26</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>96,74; 100,0</t>
+          <t>96,79; 99,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>96,28; 99,32</t>
+          <t>97,56; 100,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,32; 99,38</t>
+          <t>97,64; 99,49</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,07</t>
+          <t>97,42; 98,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>97,28; 98,82</t>
+          <t>97,54; 99,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97,68; 98,79</t>
+          <t>97,85; 98,89</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>95</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72811</t>
+          <t>63353</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78404</t>
+          <t>56066</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151215</t>
+          <t>119419</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>70983; 73282</t>
+          <t>61640; 64145</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76337; 79366</t>
+          <t>53963; 56481</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148895; 152219</t>
+          <t>117655; 120269</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>122444</t>
+          <t>110911</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>121976</t>
+          <t>96481</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244420</t>
+          <t>207392</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>117992; 124899</t>
+          <t>106346; 113432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>117157; 124815</t>
+          <t>92201; 98545</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>238477; 248744</t>
+          <t>201974; 211108</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>96</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57871</t>
+          <t>58751</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124272</t>
+          <t>114954</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56589; 58268</t>
+          <t>57453; 59064</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64206; 66782</t>
+          <t>53997; 56558</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122291; 125050</t>
+          <t>113213; 115622</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>63600</t>
+          <t>63773</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>68997</t>
+          <t>65137</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132597</t>
+          <t>128911</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60665; 65239</t>
+          <t>60381; 64804</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65074; 70241</t>
+          <t>61875; 66573</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128648; 134763</t>
+          <t>125457; 130749</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34513</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>48694</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>55828</t>
+          <t>45508</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101645</t>
+          <t>94202</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44369; 46167</t>
+          <t>47453; 48942</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54557; 56186</t>
+          <t>44299; 45766</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>99847; 102353</t>
+          <t>92705; 94708</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>170</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>120183</t>
+          <t>137657</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>151519</t>
+          <t>117967</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271702</t>
+          <t>255624</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>116122; 121719</t>
+          <t>133697; 139290</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>147487; 153426</t>
+          <t>113816; 119603</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>266966; 274384</t>
+          <t>250789; 258275</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>189</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>130413</t>
+          <t>156251</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>153337</t>
+          <t>139447</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>283750</t>
+          <t>295698</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>127330; 131619</t>
+          <t>153459; 157935</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>150249; 155000</t>
+          <t>137063; 140497</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>279961; 285895</t>
+          <t>292000; 297529</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>914</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>647654</t>
+          <t>678968</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>737181</t>
+          <t>612419</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1384834</t>
+          <t>1291387</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>641857; 651919</t>
+          <t>672766; 683176</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>730188; 741701</t>
+          <t>606483; 616045</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1375972; 1391602</t>
+          <t>1284136; 1297813</t>
         </is>
       </c>
     </row>
